--- a/data/ltb/Kayak ending rental fee.xlsx
+++ b/data/ltb/Kayak ending rental fee.xlsx
@@ -13,10 +13,10 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1782660392" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1782660392" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1782660392" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1782660392"/>
+      <pm:revision xmlns:pm="smNativeData" day="1783270450" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1783270450" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1783270450" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1783270450"/>
     </ext>
   </extLst>
 </workbook>
@@ -40,18 +40,21 @@
     <t>Balance</t>
   </si>
   <si>
+    <t>2024-06</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>rental ending evict balace</t>
+  </si>
+  <si>
+    <t>water + hydro (-644.00)</t>
+  </si>
+  <si>
     <t>2024-05</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>rental ending evict balace</t>
-  </si>
-  <si>
-    <t>water + hydro (-644.00)</t>
-  </si>
-  <si>
     <t>missing $2300.00</t>
   </si>
   <si>
@@ -161,9 +164,6 @@
   </si>
   <si>
     <t>2024-07</t>
-  </si>
-  <si>
-    <t>2024-06</t>
   </si>
   <si>
     <t>new fee $2250.00</t>
@@ -272,7 +272,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="16">
+  <numFmts count="15">
     <numFmt numFmtId="5" formatCode="#,##0\ &quot;$&quot;;\-#,##0\ &quot;$&quot;"/>
     <numFmt numFmtId="6" formatCode="#,##0\ &quot;$&quot;;[Red]\-#,##0\ &quot;$&quot;"/>
     <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;$&quot;;\-#,##0.00\ &quot;$&quot;"/>
@@ -288,7 +288,6 @@
     <numFmt numFmtId="168" formatCode="MMMM D "/>
     <numFmt numFmtId="169" formatCode="MM/DD/YYYY;@"/>
     <numFmt numFmtId="170" formatCode="[$$-1009]0.00"/>
-    <numFmt numFmtId="171" formatCode="0.00\ [$$-1009]"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -298,7 +297,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782660392" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783270450" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -313,7 +312,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1782660392" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783270450" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -335,7 +334,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782660392" type="1" fgLvl="85" fgClr="00FFFFFF" bgLvl="15" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="85" fgClr="00FFFFFF" bgLvl="15" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -346,7 +345,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782660392" type="1" fgLvl="64" fgClr="0000FF00" bgLvl="36" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="64" fgClr="0000FF00" bgLvl="36" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -357,7 +356,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782660392" type="1" fgLvl="12" fgClr="000000FF" bgLvl="88" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="12" fgClr="000000FF" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -368,7 +367,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782660392" type="1" fgLvl="12" fgClr="00FF0000" bgLvl="88" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="12" fgClr="00FF0000" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -379,7 +378,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782660392" type="1" fgLvl="12" fgClr="0000FFFF" bgLvl="88" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="12" fgClr="0000FFFF" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -390,7 +389,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782660392" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -401,7 +400,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782660392" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -412,7 +411,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782660392" type="1" fgLvl="12" fgClr="00FFFF00" bgLvl="88" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="12" fgClr="00FFFF00" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -423,7 +422,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782660392" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -434,7 +433,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1782660392" type="1" fgLvl="100" fgClr="00FFE0E0" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="100" fgClr="00FFE0E0" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -456,7 +455,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782660392"/>
+          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
         </ext>
       </extLst>
     </border>
@@ -475,7 +474,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782660392"/>
+          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
         </ext>
       </extLst>
     </border>
@@ -494,7 +493,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782660392"/>
+          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
         </ext>
       </extLst>
     </border>
@@ -513,7 +512,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782660392"/>
+          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
         </ext>
       </extLst>
     </border>
@@ -532,7 +531,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782660392"/>
+          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
         </ext>
       </extLst>
     </border>
@@ -551,7 +550,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782660392"/>
+          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
         </ext>
       </extLst>
     </border>
@@ -570,7 +569,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782660392"/>
+          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
         </ext>
       </extLst>
     </border>
@@ -589,7 +588,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782660392"/>
+          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
         </ext>
       </extLst>
     </border>
@@ -608,7 +607,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782660392"/>
+          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
         </ext>
       </extLst>
     </border>
@@ -627,7 +626,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782660392"/>
+          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
         </ext>
       </extLst>
     </border>
@@ -646,7 +645,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1782660392"/>
+          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
         </ext>
       </extLst>
     </border>
@@ -654,7 +653,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -714,7 +713,6 @@
     <xf numFmtId="165" fontId="0" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="170" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -722,10 +720,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1782660392" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1783270450" count="1">
         <pm:charStyle name="Normal" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1782660392" count="15">
+      <pm:colors xmlns:pm="smNativeData" id="1783270450" count="15">
         <pm:color name="Color 24" rgb="D9D9D9"/>
         <pm:color name="Color 25" rgb="474747"/>
         <pm:color name="Color 26" rgb="5C5CFF"/>
@@ -1051,7 +1049,7 @@
       <c r="H3" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="51" t="n">
+      <c r="J3" s="36" t="n">
         <v>-1000</v>
       </c>
       <c r="K3" s="24"/>
@@ -1166,13 +1164,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="25" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J15" s="36" t="n">
         <v>-2300</v>
       </c>
       <c r="K15" s="25" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="2:14">
@@ -1186,7 +1184,7 @@
         <v>1000</v>
       </c>
       <c r="H16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K16" s="24"/>
       <c r="L16" s="24"/>
@@ -1227,7 +1225,7 @@
         <v>1000</v>
       </c>
       <c r="H20" s="26" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K20" s="29"/>
       <c r="L20" s="29"/>
@@ -1262,7 +1260,7 @@
         <v>-165.210000000000008</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="2:14">
@@ -1276,7 +1274,7 @@
         <v>1150</v>
       </c>
       <c r="H25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K25" s="24"/>
       <c r="L25" s="24"/>
@@ -1306,7 +1304,7 @@
         <v>800</v>
       </c>
       <c r="H28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J28" s="45" t="n">
         <v>550</v>
@@ -1340,7 +1338,7 @@
         <v>-166.5</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="2:14">
@@ -1354,7 +1352,7 @@
         <v>500</v>
       </c>
       <c r="H32" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J32" s="45" t="n">
         <v>1000</v>
@@ -1407,7 +1405,7 @@
         <v>-154.349999999999994</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="2:11" s="16" customFormat="1">
@@ -1419,7 +1417,7 @@
         <v>-158.009999999999991</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="2:14">
@@ -1433,7 +1431,7 @@
         <v>500</v>
       </c>
       <c r="H39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J39" s="45" t="n">
         <v>1000</v>
@@ -1520,7 +1518,7 @@
         <v>-11925</v>
       </c>
       <c r="K46" s="16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="2:14">
@@ -1560,13 +1558,13 @@
         <v>720</v>
       </c>
       <c r="H51" s="31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J51" s="46" t="n">
         <v>-150</v>
       </c>
       <c r="K51" s="31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" spans="2:14">
@@ -1600,13 +1598,13 @@
         <v>700</v>
       </c>
       <c r="H54" s="31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J54" s="46" t="n">
         <v>-1550</v>
       </c>
       <c r="K54" s="31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="2:11" s="7" customFormat="1">
@@ -1621,7 +1619,7 @@
         <v>170</v>
       </c>
       <c r="K55" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56" spans="2:11" s="7" customFormat="1">
@@ -1634,7 +1632,7 @@
       </c>
       <c r="J56" s="11"/>
       <c r="K56" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57" spans="2:11" s="7" customFormat="1">
@@ -1647,7 +1645,7 @@
       </c>
       <c r="J57" s="11"/>
       <c r="K57" s="7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58" spans="2:11" s="31" customFormat="1">
@@ -1661,18 +1659,18 @@
         <v>1000</v>
       </c>
       <c r="H58" s="44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J58" s="46" t="n">
         <v>-1250.00250000000005</v>
       </c>
       <c r="K58" s="31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:11">
       <c r="A60" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B60" s="2" t="n">
         <v>45861</v>
@@ -1684,13 +1682,13 @@
         <v>3750</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J60" s="45" t="n">
         <v>1500</v>
       </c>
       <c r="K60" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="61" spans="1:14" s="25" customFormat="1">
@@ -1703,13 +1701,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="35" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J61" s="28" t="n">
         <v>-2250</v>
       </c>
       <c r="K61" s="25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N61" s="34"/>
     </row>
@@ -1723,13 +1721,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J62" s="28" t="n">
         <v>-2250</v>
       </c>
       <c r="K62" s="25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N62" s="34"/>
     </row>
@@ -1745,13 +1743,13 @@
         <v>1250</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J63" s="12" t="n">
         <v>150</v>
       </c>
       <c r="K63" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N63" s="43"/>
     </row>
@@ -1774,13 +1772,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="35" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J65" s="28" t="n">
         <v>-2250</v>
       </c>
       <c r="K65" s="25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -1795,7 +1793,7 @@
         <v>1250</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1819,7 +1817,7 @@
         <v>1050</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="15.40" customHeight="1">
@@ -1863,7 +1861,7 @@
         <v>1150</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73" spans="2:7">
@@ -1885,7 +1883,7 @@
         <v>1250</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="75" spans="2:7">
@@ -1907,7 +1905,7 @@
         <v>1000</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="77" spans="2:7">
@@ -1929,13 +1927,13 @@
         <v>1200</v>
       </c>
       <c r="H78" s="44" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J78" s="28" t="n">
         <v>-50</v>
       </c>
       <c r="K78" s="31" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79" spans="2:8" s="26" customFormat="1">
@@ -1947,7 +1945,7 @@
         <v>1000</v>
       </c>
       <c r="H79" s="27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="80" spans="2:11" s="25" customFormat="1">
@@ -1959,13 +1957,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J80" s="28" t="n">
         <v>-2250</v>
       </c>
       <c r="K80" s="25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81" spans="1:7" s="17" customFormat="1">
@@ -1984,7 +1982,7 @@
         <v>2250</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="83" spans="2:8">
@@ -1998,7 +1996,7 @@
         <v>1050</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>46</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="2:7">
@@ -2031,7 +2029,7 @@
         <v>750</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K86" t="s">
         <v>47</v>
@@ -2056,7 +2054,7 @@
         <v>1000</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89" spans="2:7">
@@ -2722,7 +2720,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1782660392" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783270450" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -2731,16 +2729,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1782660392" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1782660392" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1782660392" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1782660392" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1783270450" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783270450" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783270450" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783270450" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1782660392" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783270450" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/data/ltb/Kayak ending rental fee.xlsx
+++ b/data/ltb/Kayak ending rental fee.xlsx
@@ -5,25 +5,26 @@
   <fileSharing readOnlyRecommended="0" userName="KwGo"/>
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="14805" windowHeight="8010" tabRatio="500"/>
+    <workbookView activeTab="1" xWindow="240" yWindow="60" windowWidth="14805" windowHeight="8010" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Kayak" sheetId="1" r:id="rId4"/>
+    <sheet name="Kayak Rent Details" sheetId="1" r:id="rId4"/>
+    <sheet name="Rent Ledger" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1783270450" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1783270450" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1783270450" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1783270450"/>
+      <pm:revision xmlns:pm="smNativeData" day="1783280795" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1783280795" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1783280795" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1783280795"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="94">
   <si>
     <t>Paid date</t>
   </si>
@@ -40,27 +41,36 @@
     <t>Balance</t>
   </si>
   <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>rental ending evict balace</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>missing $2300.00</t>
+  </si>
+  <si>
     <t>2024-06</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t>rental ending evict balace</t>
-  </si>
-  <si>
     <t>water + hydro (-644.00)</t>
   </si>
   <si>
     <t>2024-05</t>
   </si>
   <si>
-    <t>missing $2300.00</t>
+    <t>missing $1000.00</t>
   </si>
   <si>
     <t>2024-04</t>
   </si>
   <si>
+    <t>missing $1300.00</t>
+  </si>
+  <si>
     <t>2026-03</t>
   </si>
   <si>
@@ -115,9 +125,6 @@
     <t xml:space="preserve">         </t>
   </si>
   <si>
-    <t>2025-07</t>
-  </si>
-  <si>
     <t>paid more $1500.00</t>
   </si>
   <si>
@@ -266,13 +273,46 @@
   </si>
   <si>
     <t>Deposite</t>
+  </si>
+  <si>
+    <t>Rent Ledger</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Charge</t>
+  </si>
+  <si>
+    <t>Payment</t>
+  </si>
+  <si>
+    <t>Balance Owing</t>
+  </si>
+  <si>
+    <t>Previous arrears balance</t>
+  </si>
+  <si>
+    <t>May rent charged</t>
+  </si>
+  <si>
+    <t>June rent charged</t>
+  </si>
+  <si>
+    <t>July rent charged</t>
+  </si>
+  <si>
+    <t>Final Balance Owing: $15269.00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="15">
+  <numFmts count="16">
     <numFmt numFmtId="5" formatCode="#,##0\ &quot;$&quot;;\-#,##0\ &quot;$&quot;"/>
     <numFmt numFmtId="6" formatCode="#,##0\ &quot;$&quot;;[Red]\-#,##0\ &quot;$&quot;"/>
     <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;$&quot;;\-#,##0.00\ &quot;$&quot;"/>
@@ -288,6 +328,7 @@
     <numFmt numFmtId="168" formatCode="MMMM D "/>
     <numFmt numFmtId="169" formatCode="MM/DD/YYYY;@"/>
     <numFmt numFmtId="170" formatCode="[$$-1009]0.00"/>
+    <numFmt numFmtId="171" formatCode="MM/DD/YYYY"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -297,7 +338,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783270450" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783280795" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -312,7 +353,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783270450" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783280795" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -321,7 +362,7 @@
       </extLst>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,7 +375,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="85" fgClr="00FFFFFF" bgLvl="15" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="85" fgClr="00FFFFFF" bgLvl="15" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -345,7 +386,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="64" fgClr="0000FF00" bgLvl="36" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="64" fgClr="0000FF00" bgLvl="36" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -356,7 +397,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="12" fgClr="000000FF" bgLvl="88" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="12" fgClr="000000FF" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -367,7 +408,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="12" fgClr="00FF0000" bgLvl="88" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="12" fgClr="00FF0000" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -378,7 +419,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="12" fgClr="0000FFFF" bgLvl="88" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="12" fgClr="0000FFFF" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -389,7 +430,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -400,7 +441,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -411,7 +452,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="12" fgClr="00FFFF00" bgLvl="88" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="12" fgClr="00FFFF00" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -422,7 +463,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -433,13 +474,24 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783270450" type="1" fgLvl="100" fgClr="00FFE0E0" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="100" fgClr="00FFE0E0" bgLvl="0" bgClr="00FFFFFF"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0F0E0"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="12" fgClr="007F7F00" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left style="none">
         <color rgb="FF000000"/>
@@ -455,7 +507,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
+          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
         </ext>
       </extLst>
     </border>
@@ -474,7 +526,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
+          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
         </ext>
       </extLst>
     </border>
@@ -493,7 +545,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
+          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
         </ext>
       </extLst>
     </border>
@@ -512,7 +564,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
+          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
         </ext>
       </extLst>
     </border>
@@ -531,7 +583,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
+          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
         </ext>
       </extLst>
     </border>
@@ -550,7 +602,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
+          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
         </ext>
       </extLst>
     </border>
@@ -569,7 +621,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
+          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
         </ext>
       </extLst>
     </border>
@@ -588,7 +640,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
+          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
         </ext>
       </extLst>
     </border>
@@ -607,7 +659,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
+          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
         </ext>
       </extLst>
     </border>
@@ -626,7 +678,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
+          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
         </ext>
       </extLst>
     </border>
@@ -645,7 +697,26 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783270450"/>
+          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
         </ext>
       </extLst>
     </border>
@@ -653,7 +724,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -713,6 +784,22 @@
     <xf numFmtId="165" fontId="0" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="170" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -720,10 +807,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1783270450" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1783280795" count="1">
         <pm:charStyle name="Normal" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1783270450" count="15">
+      <pm:colors xmlns:pm="smNativeData" id="1783280795" count="15">
         <pm:color name="Color 24" rgb="D9D9D9"/>
         <pm:color name="Color 25" rgb="474747"/>
         <pm:color name="Color 26" rgb="5C5CFF"/>
@@ -1001,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:N145"/>
+  <dimension ref="A1:N148"/>
   <sheetFormatPr baseColWidth="9" defaultColWidth="10.000000" defaultRowHeight="15.40"/>
   <cols>
     <col min="1" max="1" width="11.071429" customWidth="1"/>
@@ -1036,278 +1123,284 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:14">
-      <c r="B3" s="2" t="n">
+    <row r="5" spans="2:11" s="16" customFormat="1">
+      <c r="B5" s="58" t="n">
+        <v>46208</v>
+      </c>
+      <c r="D5" s="58" t="n">
+        <v>46208</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J5" s="28" t="n">
+        <v>-15269</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="25" customFormat="1">
+      <c r="A6" s="42"/>
+      <c r="B6" s="35"/>
+      <c r="E6" s="57" t="n">
+        <v>2300</v>
+      </c>
+      <c r="G6" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" s="28" t="n">
+        <v>-2300</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="N6" s="34"/>
+    </row>
+    <row r="7" spans="2:14">
+      <c r="B7" s="2" t="n">
         <v>46182</v>
       </c>
-      <c r="E3" s="24" t="n">
+      <c r="E7" s="24" t="n">
         <v>2300</v>
       </c>
-      <c r="G3" s="38" t="n">
+      <c r="G7" s="38" t="n">
         <v>500</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H7" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="J7" s="28" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+    </row>
+    <row r="8" spans="2:14">
+      <c r="B8" s="2" t="n">
+        <v>46181</v>
+      </c>
+      <c r="E8" s="24"/>
+      <c r="G8" s="38" t="n">
+        <v>800</v>
+      </c>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+    </row>
+    <row r="9" spans="2:14" s="17" customFormat="1">
+      <c r="B9" s="18"/>
+      <c r="E9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="N9" s="30"/>
+    </row>
+    <row r="11" spans="2:10" s="7" customFormat="1">
+      <c r="B11" s="9" t="n">
+        <v>45505</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>45565</v>
+      </c>
+      <c r="E11" s="50" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>2200</v>
+      </c>
+      <c r="J11" s="50" t="n">
+        <v>-2300</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" s="7" customFormat="1">
+      <c r="B12" s="9" t="n">
+        <v>45658</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>46142</v>
+      </c>
+      <c r="E12" s="50" t="n">
+        <v>36100</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>29031</v>
+      </c>
+      <c r="J12" s="50" t="n">
+        <v>-7069</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" s="7" customFormat="1">
+      <c r="B13" s="9" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>46152</v>
+      </c>
+      <c r="E13" s="50" t="n">
+        <v>2300</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J13" s="50" t="n">
+        <v>-1300</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" s="16" customFormat="1">
+      <c r="B14" s="58" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D14" s="58" t="n">
+        <v>46157</v>
+      </c>
+      <c r="I14" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="36" t="n">
+      <c r="J14" s="28" t="n">
+        <v>-10669</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" s="47" customFormat="1">
+      <c r="B17" s="48"/>
+      <c r="E17" s="49"/>
+      <c r="G17" s="49"/>
+      <c r="J17" s="49"/>
+      <c r="K17" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="L17" s="46"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
+    </row>
+    <row r="18" spans="2:14" s="17" customFormat="1">
+      <c r="B18" s="18"/>
+      <c r="E18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="N18" s="30"/>
+    </row>
+    <row r="19" spans="2:14" s="51" customFormat="1">
+      <c r="B19" s="52" t="n">
+        <v>46149</v>
+      </c>
+      <c r="E19" s="53" t="n">
+        <v>2300</v>
+      </c>
+      <c r="G19" s="43" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H19" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="J19" s="55" t="n">
+        <v>-1300</v>
+      </c>
+      <c r="K19" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="L19" s="53"/>
+      <c r="M19" s="53"/>
+      <c r="N19" s="53"/>
+    </row>
+    <row r="20" spans="2:13">
+      <c r="B20" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="G20" s="38" t="n">
+        <v>800</v>
+      </c>
+      <c r="H20" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="55" t="n">
         <v>-1000</v>
       </c>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-    </row>
-    <row r="4" spans="2:14">
-      <c r="B4" s="2" t="n">
-        <v>46181</v>
-      </c>
-      <c r="E4" s="24"/>
-      <c r="G4" s="38" t="n">
-        <v>800</v>
-      </c>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-    </row>
-    <row r="5" spans="2:14" s="17" customFormat="1">
-      <c r="B5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="N5" s="30"/>
-    </row>
-    <row r="7" spans="2:10" s="7" customFormat="1">
-      <c r="B7" s="9" t="n">
-        <v>45505</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>45565</v>
-      </c>
-      <c r="E7" s="50" t="n">
-        <v>4500</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <v>2200</v>
-      </c>
-      <c r="J7" s="50" t="n">
-        <v>-2300</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" s="7" customFormat="1">
-      <c r="B8" s="9" t="n">
-        <v>45658</v>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>46142</v>
-      </c>
-      <c r="E8" s="50" t="n">
-        <v>36100</v>
-      </c>
-      <c r="G8" s="8" t="n">
-        <v>29031</v>
-      </c>
-      <c r="J8" s="50" t="n">
-        <v>-7069</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" s="7" customFormat="1">
-      <c r="B9" s="9" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D9" s="9" t="n">
-        <v>46152</v>
-      </c>
-      <c r="E9" s="50" t="n">
-        <v>2300</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J9" s="50" t="n">
-        <v>-1300</v>
-      </c>
-    </row>
-    <row r="10" spans="9:11" s="16" customFormat="1">
-      <c r="I10" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="J10" s="28" t="n">
-        <v>-10669</v>
-      </c>
-      <c r="K10" s="16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="2:14" s="47" customFormat="1">
-      <c r="B13" s="48"/>
-      <c r="E13" s="49"/>
-      <c r="G13" s="49"/>
-      <c r="J13" s="49"/>
-      <c r="K13" s="46" t="s">
-        <v>8</v>
-      </c>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="46"/>
-    </row>
-    <row r="14" spans="2:14" s="17" customFormat="1">
-      <c r="B14" s="18"/>
-      <c r="E14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="N14" s="30"/>
-    </row>
-    <row r="15" spans="5:11" s="25" customFormat="1">
-      <c r="E15" s="36" t="n">
-        <v>2300</v>
-      </c>
-      <c r="G15" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15" s="36" t="n">
-        <v>-2300</v>
-      </c>
-      <c r="K15" s="25" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="2:14">
-      <c r="B16" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="E16" s="24" t="n">
-        <v>2300</v>
-      </c>
-      <c r="G16" s="38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H16" t="s">
-        <v>11</v>
-      </c>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-    </row>
-    <row r="17" spans="2:13">
-      <c r="B17" s="2" t="n">
-        <v>46132</v>
-      </c>
-      <c r="G17" s="38" t="n">
-        <v>800</v>
-      </c>
-      <c r="K17" s="29"/>
-      <c r="L17" s="29"/>
-      <c r="M17" s="29"/>
-    </row>
-    <row r="18" spans="2:7">
-      <c r="B18" s="2" t="n">
-        <v>46125</v>
-      </c>
-      <c r="G18" s="38" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7">
-      <c r="B19" s="2"/>
-      <c r="G19" s="38"/>
-    </row>
-    <row r="20" spans="2:14" s="26" customFormat="1">
-      <c r="B20" s="27" t="n">
-        <v>46121</v>
-      </c>
-      <c r="E20" s="30" t="n">
-        <v>2300</v>
-      </c>
-      <c r="G20" s="38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H20" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="K20" s="29"/>
+      <c r="K20" s="36" t="s">
+        <v>14</v>
+      </c>
       <c r="L20" s="29"/>
       <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-    </row>
-    <row r="21" spans="2:7" s="26" customFormat="1">
-      <c r="B21" s="27" t="n">
+    </row>
+    <row r="21" spans="2:7">
+      <c r="B21" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="G21" s="38" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
+      <c r="B22" s="2"/>
+      <c r="G22" s="38"/>
+    </row>
+    <row r="23" spans="2:14" s="26" customFormat="1">
+      <c r="B23" s="27" t="n">
+        <v>46121</v>
+      </c>
+      <c r="E23" s="30" t="n">
+        <v>2300</v>
+      </c>
+      <c r="G23" s="38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H23" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+    </row>
+    <row r="24" spans="2:7" s="26" customFormat="1">
+      <c r="B24" s="27" t="n">
         <v>46112</v>
       </c>
-      <c r="G21" s="38" t="n">
+      <c r="G24" s="38" t="n">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="2:7" s="26" customFormat="1">
-      <c r="B22" s="27" t="n">
+    <row r="25" spans="2:7" s="26" customFormat="1">
+      <c r="B25" s="27" t="n">
         <v>46099</v>
       </c>
-      <c r="G22" s="38" t="n">
+      <c r="G25" s="38" t="n">
         <v>1000</v>
       </c>
     </row>
-    <row r="23" spans="2:7" s="26" customFormat="1">
-      <c r="B23" s="27"/>
-      <c r="G23" s="38"/>
-    </row>
-    <row r="24" spans="2:11" s="16" customFormat="1">
-      <c r="B24" s="15" t="n">
+    <row r="26" spans="2:7" s="26" customFormat="1">
+      <c r="B26" s="27"/>
+      <c r="G26" s="38"/>
+    </row>
+    <row r="27" spans="2:11" s="16" customFormat="1">
+      <c r="B27" s="15" t="n">
         <v>46095</v>
       </c>
-      <c r="J24" s="28" t="n">
+      <c r="J27" s="28" t="n">
         <v>-165.210000000000008</v>
       </c>
-      <c r="K24" s="16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14">
-      <c r="B25" s="2" t="n">
-        <v>46090</v>
-      </c>
-      <c r="E25" s="24" t="n">
-        <v>2250</v>
-      </c>
-      <c r="G25" s="38" t="n">
-        <v>1150</v>
-      </c>
-      <c r="H25" t="s">
-        <v>14</v>
-      </c>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-    </row>
-    <row r="26" spans="2:7">
-      <c r="B26" s="2" t="n">
-        <v>46079</v>
-      </c>
-      <c r="G26" s="38" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7">
-      <c r="B27" s="2"/>
-      <c r="G27" s="38"/>
+      <c r="K27" s="16" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="28" spans="2:14">
       <c r="B28" s="2" t="n">
-        <v>46063</v>
+        <v>46090</v>
       </c>
       <c r="E28" s="24" t="n">
         <v>2250</v>
       </c>
       <c r="G28" s="38" t="n">
-        <v>800</v>
+        <v>1150</v>
       </c>
       <c r="H28" t="s">
-        <v>15</v>
-      </c>
-      <c r="J28" s="45" t="n">
-        <v>550</v>
+        <v>17</v>
       </c>
       <c r="K28" s="24"/>
       <c r="L28" s="24"/>
@@ -1316,475 +1409,464 @@
     </row>
     <row r="29" spans="2:7">
       <c r="B29" s="2" t="n">
-        <v>46055</v>
+        <v>46079</v>
       </c>
       <c r="G29" s="38" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="30" spans="2:7">
-      <c r="B30" s="2" t="n">
+      <c r="B30" s="2"/>
+      <c r="G30" s="38"/>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31" s="2" t="n">
+        <v>46063</v>
+      </c>
+      <c r="E31" s="24" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G31" s="38" t="n">
+        <v>800</v>
+      </c>
+      <c r="H31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J31" s="45" t="n">
+        <v>550</v>
+      </c>
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+      <c r="M31" s="24"/>
+      <c r="N31" s="24"/>
+    </row>
+    <row r="32" spans="2:7">
+      <c r="B32" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="G32" s="38" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7">
+      <c r="B33" s="2" t="n">
         <v>46048</v>
       </c>
-      <c r="G30" s="38" t="n">
+      <c r="G33" s="38" t="n">
         <v>1000</v>
       </c>
     </row>
-    <row r="31" spans="2:11" s="16" customFormat="1">
-      <c r="B31" s="15" t="n">
+    <row r="34" spans="2:11" s="16" customFormat="1">
+      <c r="B34" s="15" t="n">
         <v>46040</v>
       </c>
-      <c r="J31" s="28" t="n">
+      <c r="J34" s="28" t="n">
         <v>-166.5</v>
       </c>
-      <c r="K31" s="16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="32" spans="2:14">
-      <c r="B32" s="2" t="n">
+      <c r="K34" s="16" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14">
+      <c r="B35" s="2" t="n">
         <v>46024</v>
       </c>
-      <c r="E32" s="24" t="n">
+      <c r="E35" s="24" t="n">
         <v>2250</v>
       </c>
-      <c r="G32" s="38" t="n">
+      <c r="G35" s="38" t="n">
         <v>500</v>
       </c>
-      <c r="H32" t="s">
+      <c r="H35" t="s">
+        <v>19</v>
+      </c>
+      <c r="J35" s="45" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
+      <c r="N35" s="24"/>
+    </row>
+    <row r="36" spans="2:14" s="17" customFormat="1">
+      <c r="B36" s="18"/>
+      <c r="E36" s="30"/>
+      <c r="G36" s="19"/>
+      <c r="J36" s="30"/>
+      <c r="K36" s="30"/>
+      <c r="L36" s="30"/>
+      <c r="M36" s="30"/>
+      <c r="N36" s="30"/>
+    </row>
+    <row r="37" spans="2:7">
+      <c r="B37" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="G37" s="38" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7">
+      <c r="B38" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="G38" s="38" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7">
+      <c r="B39" s="2" t="n">
+        <v>45999</v>
+      </c>
+      <c r="G39" s="38" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" s="16" customFormat="1">
+      <c r="B40" s="15" t="n">
+        <v>45988</v>
+      </c>
+      <c r="E40" s="14"/>
+      <c r="J40" s="28" t="n">
+        <v>-154.349999999999994</v>
+      </c>
+      <c r="K40" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="J32" s="45" t="n">
+    </row>
+    <row r="41" spans="2:11" s="16" customFormat="1">
+      <c r="B41" s="15" t="n">
+        <v>45988</v>
+      </c>
+      <c r="E41" s="14"/>
+      <c r="J41" s="28" t="n">
+        <v>-158.009999999999991</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14">
+      <c r="B42" s="2" t="n">
+        <v>45987</v>
+      </c>
+      <c r="E42" s="24" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G42" s="38" t="n">
+        <v>500</v>
+      </c>
+      <c r="H42" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" s="45" t="n">
         <v>1000</v>
       </c>
-      <c r="K32" s="24"/>
-      <c r="L32" s="24"/>
-      <c r="M32" s="24"/>
-      <c r="N32" s="24"/>
-    </row>
-    <row r="33" spans="2:14" s="17" customFormat="1">
-      <c r="B33" s="18"/>
-      <c r="E33" s="30"/>
-      <c r="G33" s="19"/>
-      <c r="J33" s="30"/>
-      <c r="K33" s="30"/>
-      <c r="L33" s="30"/>
-      <c r="M33" s="30"/>
-      <c r="N33" s="30"/>
-    </row>
-    <row r="34" spans="2:7">
-      <c r="B34" s="2" t="n">
-        <v>46021</v>
-      </c>
-      <c r="G34" s="38" t="n">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7">
-      <c r="B35" s="2" t="n">
-        <v>46008</v>
-      </c>
-      <c r="G35" s="38" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7">
-      <c r="B36" s="2" t="n">
-        <v>45999</v>
-      </c>
-      <c r="G36" s="38" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="37" spans="2:11" s="16" customFormat="1">
-      <c r="B37" s="15" t="n">
-        <v>45988</v>
-      </c>
-      <c r="E37" s="14"/>
-      <c r="J37" s="28" t="n">
-        <v>-154.349999999999994</v>
-      </c>
-      <c r="K37" s="16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11" s="16" customFormat="1">
-      <c r="B38" s="15" t="n">
-        <v>45988</v>
-      </c>
-      <c r="E38" s="14"/>
-      <c r="J38" s="28" t="n">
-        <v>-158.009999999999991</v>
-      </c>
-      <c r="K38" s="16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39" spans="2:14">
-      <c r="B39" s="2" t="n">
-        <v>45987</v>
-      </c>
-      <c r="E39" s="24" t="n">
+      <c r="M42" s="45"/>
+      <c r="N42" s="24"/>
+    </row>
+    <row r="43" spans="2:13">
+      <c r="B43" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="G43" s="38" t="n">
+        <v>500</v>
+      </c>
+      <c r="K43" s="24"/>
+      <c r="L43" s="24"/>
+      <c r="M43" s="24"/>
+    </row>
+    <row r="44" spans="2:7">
+      <c r="B44" s="2" t="n">
+        <v>45985</v>
+      </c>
+      <c r="G44" s="38" t="n">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" s="0" customFormat="1"/>
+    <row r="46" spans="2:10" s="7" customFormat="1">
+      <c r="B46" s="9" t="n">
+        <v>45505</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>45565</v>
+      </c>
+      <c r="E46" s="50" t="n">
+        <v>4500</v>
+      </c>
+      <c r="G46" s="8" t="n">
+        <v>2200</v>
+      </c>
+      <c r="J46" s="50" t="n">
+        <v>-2300</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" s="7" customFormat="1">
+      <c r="B47" s="9" t="n">
+        <v>45658</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>45961</v>
+      </c>
+      <c r="E47" s="50" t="n">
+        <v>22500</v>
+      </c>
+      <c r="G47" s="8" t="n">
+        <v>14620</v>
+      </c>
+      <c r="J47" s="50" t="n">
+        <v>-7880</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" s="7" customFormat="1">
+      <c r="B48" s="9" t="n">
+        <v>45962</v>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>45991</v>
+      </c>
+      <c r="E48" s="50" t="n">
         <v>2250</v>
       </c>
-      <c r="G39" s="38" t="n">
-        <v>500</v>
-      </c>
-      <c r="H39" t="s">
-        <v>18</v>
-      </c>
-      <c r="J39" s="45" t="n">
-        <v>1000</v>
-      </c>
-      <c r="M39" s="45"/>
-      <c r="N39" s="24"/>
-    </row>
-    <row r="40" spans="2:13">
-      <c r="B40" s="2" t="n">
-        <v>45985</v>
-      </c>
-      <c r="G40" s="38" t="n">
-        <v>500</v>
-      </c>
-      <c r="K40" s="24"/>
-      <c r="L40" s="24"/>
-      <c r="M40" s="24"/>
-    </row>
-    <row r="41" spans="2:7">
-      <c r="B41" s="2" t="n">
-        <v>45985</v>
-      </c>
-      <c r="G41" s="38" t="n">
-        <v>1750</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" s="0" customFormat="1"/>
-    <row r="43" spans="2:10" s="7" customFormat="1">
-      <c r="B43" s="9" t="n">
-        <v>45505</v>
-      </c>
-      <c r="D43" s="9" t="n">
-        <v>45565</v>
-      </c>
-      <c r="E43" s="50" t="n">
-        <v>4500</v>
-      </c>
-      <c r="G43" s="8" t="n">
-        <v>2200</v>
-      </c>
-      <c r="J43" s="50" t="n">
-        <v>-2300</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10" s="7" customFormat="1">
-      <c r="B44" s="9" t="n">
-        <v>45658</v>
-      </c>
-      <c r="D44" s="9" t="n">
-        <v>45961</v>
-      </c>
-      <c r="E44" s="50" t="n">
-        <v>22500</v>
-      </c>
-      <c r="G44" s="8" t="n">
-        <v>14620</v>
-      </c>
-      <c r="J44" s="50" t="n">
-        <v>-7880</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10" s="7" customFormat="1">
-      <c r="B45" s="9" t="n">
-        <v>45962</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>45991</v>
-      </c>
-      <c r="E45" s="50" t="n">
-        <v>2250</v>
-      </c>
-      <c r="G45" s="8" t="n">
+      <c r="G48" s="8" t="n">
         <v>505</v>
       </c>
-      <c r="J45" s="50" t="n">
+      <c r="J48" s="50" t="n">
         <v>-1745</v>
       </c>
     </row>
-    <row r="46" spans="9:11" s="16" customFormat="1">
-      <c r="I46" s="23" t="s">
-        <v>6</v>
-      </c>
-      <c r="J46" s="28" t="n">
+    <row r="49" spans="2:11" s="16" customFormat="1">
+      <c r="B49" s="58" t="n">
+        <v>46333</v>
+      </c>
+      <c r="D49" s="58" t="n">
+        <v>46333</v>
+      </c>
+      <c r="I49" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="J49" s="28" t="n">
         <v>-11925</v>
       </c>
-      <c r="K46" s="16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="48" spans="2:14">
-      <c r="B48" s="2" t="n">
+      <c r="K49" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="51" spans="2:14">
+      <c r="B51" s="2" t="n">
         <v>45965</v>
       </c>
-      <c r="E48" s="1"/>
-      <c r="G48" s="43" t="n">
+      <c r="E51" s="1"/>
+      <c r="G51" s="43" t="n">
         <v>505</v>
       </c>
-      <c r="J48" s="38"/>
-      <c r="K48" s="24"/>
-      <c r="L48" s="24"/>
-      <c r="M48" s="24"/>
-      <c r="N48" s="29"/>
-    </row>
-    <row r="49" spans="2:14" s="17" customFormat="1">
-      <c r="B49" s="18"/>
-      <c r="E49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="N49" s="30"/>
-    </row>
-    <row r="50" spans="2:14" s="26" customFormat="1">
-      <c r="B50" s="27"/>
-      <c r="E50" s="38"/>
-      <c r="G50" s="38"/>
-      <c r="N50" s="29"/>
-    </row>
-    <row r="51" spans="2:11" s="31" customFormat="1">
-      <c r="B51" s="44" t="n">
-        <v>45961</v>
-      </c>
-      <c r="E51" s="32" t="n">
-        <v>2250</v>
-      </c>
-      <c r="G51" s="32" t="n">
-        <v>720</v>
-      </c>
-      <c r="H51" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="J51" s="46" t="n">
-        <v>-150</v>
-      </c>
-      <c r="K51" s="31" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52" spans="2:14">
-      <c r="B52" s="2" t="n">
-        <v>45950</v>
-      </c>
-      <c r="E52" s="1"/>
-      <c r="G52" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H52" s="2"/>
-      <c r="N52" s="39"/>
-    </row>
-    <row r="53" spans="2:7">
-      <c r="B53" s="2" t="n">
-        <v>45939</v>
-      </c>
-      <c r="E53" s="1"/>
-      <c r="G53" s="1" t="n">
-        <v>380</v>
-      </c>
+      <c r="J51" s="38"/>
+      <c r="K51" s="24"/>
+      <c r="L51" s="24"/>
+      <c r="M51" s="24"/>
+      <c r="N51" s="29"/>
+    </row>
+    <row r="52" spans="2:14" s="17" customFormat="1">
+      <c r="B52" s="18"/>
+      <c r="E52" s="19"/>
+      <c r="G52" s="19"/>
+      <c r="N52" s="30"/>
+    </row>
+    <row r="53" spans="2:14" s="26" customFormat="1">
+      <c r="B53" s="27"/>
+      <c r="E53" s="38"/>
+      <c r="G53" s="38"/>
+      <c r="N53" s="29"/>
     </row>
     <row r="54" spans="2:11" s="31" customFormat="1">
       <c r="B54" s="44" t="n">
-        <v>45937</v>
+        <v>45961</v>
       </c>
       <c r="E54" s="32" t="n">
         <v>2250</v>
       </c>
       <c r="G54" s="32" t="n">
+        <v>720</v>
+      </c>
+      <c r="H54" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="J54" s="46" t="n">
+        <v>-150</v>
+      </c>
+      <c r="K54" s="31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="2:14">
+      <c r="B55" s="2" t="n">
+        <v>45950</v>
+      </c>
+      <c r="E55" s="1"/>
+      <c r="G55" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H55" s="2"/>
+      <c r="N55" s="39"/>
+    </row>
+    <row r="56" spans="2:7">
+      <c r="B56" s="2" t="n">
+        <v>45939</v>
+      </c>
+      <c r="E56" s="1"/>
+      <c r="G56" s="1" t="n">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" s="31" customFormat="1">
+      <c r="B57" s="44" t="n">
+        <v>45937</v>
+      </c>
+      <c r="E57" s="32" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G57" s="32" t="n">
         <v>700</v>
       </c>
-      <c r="H54" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="J54" s="46" t="n">
+      <c r="H57" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="J57" s="46" t="n">
         <v>-1550</v>
       </c>
-      <c r="K54" s="31" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11" s="7" customFormat="1">
-      <c r="B55" s="9" t="n">
+      <c r="K57" s="31" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" s="7" customFormat="1">
+      <c r="B58" s="9" t="n">
         <v>45919</v>
       </c>
-      <c r="E55" s="8"/>
-      <c r="G55" s="8" t="n">
+      <c r="E58" s="8"/>
+      <c r="G58" s="8" t="n">
         <v>1000</v>
       </c>
-      <c r="J55" s="12" t="n">
+      <c r="J58" s="12" t="n">
         <v>170</v>
       </c>
-      <c r="K55" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11" s="7" customFormat="1">
-      <c r="B56" s="9" t="n">
+      <c r="K58" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" s="7" customFormat="1">
+      <c r="B59" s="9" t="n">
         <v>45908</v>
       </c>
-      <c r="E56" s="8"/>
-      <c r="G56" s="8" t="n">
+      <c r="E59" s="8"/>
+      <c r="G59" s="8" t="n">
         <v>800</v>
       </c>
-      <c r="J56" s="11"/>
-      <c r="K56" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="57" spans="2:11" s="7" customFormat="1">
-      <c r="B57" s="9" t="n">
+      <c r="J59" s="11"/>
+      <c r="K59" s="7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" s="7" customFormat="1">
+      <c r="B60" s="9" t="n">
         <v>45888</v>
       </c>
-      <c r="E57" s="8"/>
-      <c r="G57" s="8" t="n">
+      <c r="E60" s="8"/>
+      <c r="G60" s="8" t="n">
         <v>700</v>
       </c>
-      <c r="J57" s="11"/>
-      <c r="K57" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="58" spans="2:11" s="31" customFormat="1">
-      <c r="B58" s="44" t="n">
+      <c r="J60" s="11"/>
+      <c r="K60" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" s="31" customFormat="1">
+      <c r="B61" s="44" t="n">
         <v>45882</v>
       </c>
-      <c r="E58" s="32" t="n">
+      <c r="E61" s="32" t="n">
         <v>2250</v>
       </c>
-      <c r="G58" s="32" t="n">
+      <c r="G61" s="32" t="n">
         <v>1000</v>
       </c>
-      <c r="H58" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="J58" s="46" t="n">
+      <c r="H61" s="44" t="s">
+        <v>30</v>
+      </c>
+      <c r="J61" s="46" t="n">
         <v>-1250.00250000000005</v>
       </c>
-      <c r="K58" s="31" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
-      <c r="A60" t="s">
-        <v>29</v>
-      </c>
-      <c r="B60" s="2" t="n">
+      <c r="K61" s="31" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" t="s">
+        <v>32</v>
+      </c>
+      <c r="B63" s="2" t="n">
         <v>45861</v>
-      </c>
-      <c r="E60" s="1" t="n">
-        <v>2250</v>
-      </c>
-      <c r="G60" s="1" t="n">
-        <v>3750</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J60" s="45" t="n">
-        <v>1500</v>
-      </c>
-      <c r="K60" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14" s="25" customFormat="1">
-      <c r="A61" s="42"/>
-      <c r="B61" s="35"/>
-      <c r="E61" s="34" t="n">
-        <v>2250</v>
-      </c>
-      <c r="G61" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="J61" s="28" t="n">
-        <v>-2250</v>
-      </c>
-      <c r="K61" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="N61" s="34"/>
-    </row>
-    <row r="62" spans="1:14" s="25" customFormat="1">
-      <c r="A62" s="42"/>
-      <c r="B62" s="35"/>
-      <c r="E62" s="34" t="n">
-        <v>2250</v>
-      </c>
-      <c r="G62" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="J62" s="28" t="n">
-        <v>-2250</v>
-      </c>
-      <c r="K62" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="N62" s="34"/>
-    </row>
-    <row r="63" spans="1:14">
-      <c r="A63" s="5"/>
-      <c r="B63" s="2" t="n">
-        <v>45784</v>
       </c>
       <c r="E63" s="1" t="n">
         <v>2250</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>1250</v>
+        <v>3750</v>
       </c>
       <c r="H63" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J63" s="45" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K63" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14" s="25" customFormat="1">
+      <c r="A64" s="42"/>
+      <c r="B64" s="35"/>
+      <c r="E64" s="34" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G64" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="J64" s="28" t="n">
+        <v>-2250</v>
+      </c>
+      <c r="K64" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="J63" s="12" t="n">
-        <v>150</v>
-      </c>
-      <c r="K63" t="s">
-        <v>36</v>
-      </c>
-      <c r="N63" s="43"/>
-    </row>
-    <row r="64" spans="1:7">
-      <c r="A64" s="5"/>
-      <c r="B64" s="2" t="n">
-        <v>45775</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" s="25" customFormat="1">
-      <c r="A65" s="41"/>
+      <c r="N64" s="34"/>
+    </row>
+    <row r="65" spans="1:14" s="25" customFormat="1">
+      <c r="A65" s="42"/>
       <c r="B65" s="35"/>
       <c r="E65" s="34" t="n">
         <v>2250</v>
       </c>
-      <c r="G65" s="34" t="n">
+      <c r="G65" s="36" t="n">
         <v>0</v>
       </c>
       <c r="H65" s="35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J65" s="28" t="n">
         <v>-2250</v>
       </c>
       <c r="K65" s="25" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
-      <c r="A66" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="N65" s="34"/>
+    </row>
+    <row r="66" spans="1:14">
+      <c r="A66" s="5"/>
       <c r="B66" s="2" t="n">
-        <v>45753</v>
+        <v>45784</v>
       </c>
       <c r="E66" s="1" t="n">
         <v>2250</v>
@@ -1793,359 +1875,380 @@
         <v>1250</v>
       </c>
       <c r="H66" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="J66" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="K66" t="s">
         <v>38</v>
       </c>
+      <c r="N66" s="43"/>
     </row>
     <row r="67" spans="1:7">
-      <c r="A67" s="4"/>
+      <c r="A67" s="5"/>
       <c r="B67" s="2" t="n">
+        <v>45775</v>
+      </c>
+      <c r="G67" s="1" t="n">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" s="25" customFormat="1">
+      <c r="A68" s="41"/>
+      <c r="B68" s="35"/>
+      <c r="E68" s="34" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G68" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="J68" s="28" t="n">
+        <v>-2250</v>
+      </c>
+      <c r="K68" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="3"/>
+      <c r="B69" s="2" t="n">
+        <v>45753</v>
+      </c>
+      <c r="E69" s="1" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G69" s="1" t="n">
+        <v>1250</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" s="4"/>
+      <c r="B70" s="2" t="n">
         <v>45714</v>
       </c>
-      <c r="G67" s="1" t="n">
+      <c r="G70" s="1" t="n">
         <v>1000</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
-      <c r="A68" s="3"/>
-      <c r="B68" s="2" t="n">
+    <row r="71" spans="1:8">
+      <c r="A71" s="3"/>
+      <c r="B71" s="2" t="n">
         <v>45693</v>
       </c>
-      <c r="E68" s="1" t="n">
+      <c r="E71" s="1" t="n">
         <v>2250</v>
       </c>
-      <c r="G68" s="1" t="n">
+      <c r="G71" s="1" t="n">
         <v>1050</v>
       </c>
-      <c r="H68" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="15.40" customHeight="1">
-      <c r="A69" s="4"/>
-      <c r="B69" s="2" t="n">
+      <c r="H71" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="15.40" customHeight="1">
+      <c r="A72" s="4"/>
+      <c r="B72" s="2" t="n">
         <v>45684</v>
       </c>
-      <c r="G69" s="1" t="n">
+      <c r="G72" s="1" t="n">
         <v>1200</v>
       </c>
     </row>
-    <row r="70" spans="1:7" s="17" customFormat="1">
-      <c r="A70" s="40"/>
-      <c r="B70" s="18"/>
-      <c r="G70" s="19"/>
-    </row>
-    <row r="71" spans="2:14" s="47" customFormat="1">
-      <c r="B71" s="48"/>
-      <c r="E71" s="49"/>
-      <c r="G71" s="49"/>
-      <c r="J71" s="49"/>
-      <c r="K71" s="46"/>
-      <c r="L71" s="46" t="n">
+    <row r="73" spans="1:7" s="17" customFormat="1">
+      <c r="A73" s="40"/>
+      <c r="B73" s="18"/>
+      <c r="G73" s="19"/>
+    </row>
+    <row r="74" spans="2:14" s="47" customFormat="1">
+      <c r="B74" s="48"/>
+      <c r="E74" s="49"/>
+      <c r="G74" s="49"/>
+      <c r="J74" s="49"/>
+      <c r="K74" s="46"/>
+      <c r="L74" s="46" t="n">
         <v>-4500</v>
       </c>
-      <c r="M71" s="46" t="n">
+      <c r="M74" s="46" t="n">
         <v>2200</v>
       </c>
-      <c r="N71" s="46" t="n">
+      <c r="N74" s="46" t="n">
         <v>-2300</v>
       </c>
     </row>
-    <row r="72" spans="2:8">
-      <c r="B72" s="2" t="n">
+    <row r="75" spans="2:8">
+      <c r="B75" s="2" t="n">
         <v>45645</v>
       </c>
-      <c r="E72" s="1" t="n">
+      <c r="E75" s="1" t="n">
         <v>2250</v>
       </c>
-      <c r="G72" s="1" t="n">
+      <c r="G75" s="1" t="n">
         <v>1150</v>
       </c>
-      <c r="H72" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="73" spans="2:7">
-      <c r="B73" s="2" t="n">
+      <c r="H75" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7">
+      <c r="B76" s="2" t="n">
         <v>45634</v>
       </c>
-      <c r="G73" s="1" t="n">
+      <c r="G76" s="1" t="n">
         <v>1100</v>
       </c>
     </row>
-    <row r="74" spans="2:8">
-      <c r="B74" s="2" t="n">
+    <row r="77" spans="2:8">
+      <c r="B77" s="2" t="n">
         <v>45616</v>
       </c>
-      <c r="E74" s="1" t="n">
+      <c r="E77" s="1" t="n">
         <v>2250</v>
-      </c>
-      <c r="G74" s="1" t="n">
-        <v>1250</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="75" spans="2:7">
-      <c r="B75" s="2" t="n">
-        <v>45602</v>
-      </c>
-      <c r="G75" s="1" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="76" spans="2:8">
-      <c r="B76" s="2" t="n">
-        <v>45580</v>
-      </c>
-      <c r="E76" s="1" t="n">
-        <v>2250</v>
-      </c>
-      <c r="G76" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="77" spans="2:7">
-      <c r="B77" s="2" t="n">
-        <v>45570</v>
       </c>
       <c r="G77" s="1" t="n">
         <v>1250</v>
       </c>
-    </row>
-    <row r="78" spans="2:11" s="31" customFormat="1">
-      <c r="B78" s="44" t="n">
+      <c r="H77" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="78" spans="2:7">
+      <c r="B78" s="2" t="n">
+        <v>45602</v>
+      </c>
+      <c r="G78" s="1" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="79" spans="2:8">
+      <c r="B79" s="2" t="n">
+        <v>45580</v>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G79" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7">
+      <c r="B80" s="2" t="n">
+        <v>45570</v>
+      </c>
+      <c r="G80" s="1" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11" s="31" customFormat="1">
+      <c r="B81" s="44" t="n">
         <v>45540</v>
       </c>
-      <c r="E78" s="32" t="n">
+      <c r="E81" s="32" t="n">
         <v>2250</v>
       </c>
-      <c r="G78" s="32" t="n">
+      <c r="G81" s="32" t="n">
         <v>1200</v>
       </c>
-      <c r="H78" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="J78" s="28" t="n">
+      <c r="H81" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="J81" s="28" t="n">
         <v>-50</v>
       </c>
-      <c r="K78" s="31" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="79" spans="2:8" s="26" customFormat="1">
-      <c r="B79" s="27" t="n">
+      <c r="K81" s="31" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="82" spans="2:8" s="26" customFormat="1">
+      <c r="B82" s="27" t="n">
         <v>45532</v>
       </c>
-      <c r="E79" s="38"/>
-      <c r="G79" s="38" t="n">
+      <c r="E82" s="38"/>
+      <c r="G82" s="38" t="n">
         <v>1000</v>
       </c>
-      <c r="H79" s="27" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11" s="25" customFormat="1">
-      <c r="B80" s="35"/>
-      <c r="E80" s="34" t="n">
+      <c r="H82" s="27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11" s="25" customFormat="1">
+      <c r="B83" s="35"/>
+      <c r="E83" s="34" t="n">
         <v>2250</v>
       </c>
-      <c r="G80" s="36" t="n">
+      <c r="G83" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="H80" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="J80" s="28" t="n">
+      <c r="H83" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="J83" s="28" t="n">
         <v>-2250</v>
       </c>
-      <c r="K80" s="25" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" s="17" customFormat="1">
-      <c r="A81" s="40"/>
-      <c r="B81" s="18"/>
-      <c r="G81" s="19"/>
-    </row>
-    <row r="82" spans="2:8" s="0" customFormat="1">
-      <c r="B82" s="2" t="n">
+      <c r="K83" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" s="17" customFormat="1">
+      <c r="A84" s="40"/>
+      <c r="B84" s="18"/>
+      <c r="G84" s="19"/>
+    </row>
+    <row r="85" spans="2:8" s="0" customFormat="1">
+      <c r="B85" s="2" t="n">
         <v>45507</v>
       </c>
-      <c r="E82" s="1" t="n">
+      <c r="E85" s="1" t="n">
         <v>2250</v>
       </c>
-      <c r="G82" s="1" t="n">
+      <c r="G85" s="1" t="n">
         <v>2250</v>
       </c>
-      <c r="H82" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="83" spans="2:8">
-      <c r="B83" s="2" t="n">
+      <c r="H85" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="86" spans="2:8">
+      <c r="B86" s="2" t="n">
         <v>45475</v>
       </c>
-      <c r="E83" s="1" t="n">
+      <c r="E86" s="1" t="n">
         <v>2250</v>
       </c>
-      <c r="G83" s="1" t="n">
+      <c r="G86" s="1" t="n">
         <v>1050</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="2:7">
-      <c r="B84" s="2" t="n">
-        <v>45470</v>
-      </c>
-      <c r="E84" s="1"/>
-      <c r="G84" s="1" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="85" spans="2:8">
-      <c r="B85" s="2" t="n">
-        <v>45470</v>
-      </c>
-      <c r="E85" s="1"/>
-      <c r="G85" s="1" t="n">
-        <v>200</v>
-      </c>
-      <c r="H85" s="2"/>
-    </row>
-    <row r="86" spans="2:11">
-      <c r="B86" s="2" t="n">
-        <v>45443</v>
-      </c>
-      <c r="E86" s="19" t="n">
-        <v>2250</v>
-      </c>
-      <c r="G86" s="1" t="n">
-        <v>750</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K86" t="s">
-        <v>47</v>
-      </c>
     </row>
     <row r="87" spans="2:7">
       <c r="B87" s="2" t="n">
-        <v>45439</v>
-      </c>
+        <v>45470</v>
+      </c>
+      <c r="E87" s="1"/>
       <c r="G87" s="1" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="88" spans="2:8">
       <c r="B88" s="2" t="n">
+        <v>45470</v>
+      </c>
+      <c r="E88" s="1"/>
+      <c r="G88" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="H88" s="2"/>
+    </row>
+    <row r="89" spans="2:11">
+      <c r="B89" s="2" t="n">
+        <v>45443</v>
+      </c>
+      <c r="E89" s="19" t="n">
+        <v>2250</v>
+      </c>
+      <c r="G89" s="1" t="n">
+        <v>750</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K89" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7">
+      <c r="B90" s="2" t="n">
+        <v>45439</v>
+      </c>
+      <c r="G90" s="1" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8">
+      <c r="B91" s="2" t="n">
         <v>45404</v>
       </c>
-      <c r="E88" s="1" t="n">
+      <c r="E91" s="1" t="n">
         <v>2200</v>
       </c>
-      <c r="G88" s="1" t="n">
+      <c r="G91" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="H88" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="89" spans="2:7">
-      <c r="B89" s="2" t="n">
+      <c r="H91" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="92" spans="2:7">
+      <c r="B92" s="2" t="n">
         <v>45394</v>
       </c>
-      <c r="G89" s="1" t="n">
+      <c r="G92" s="1" t="n">
         <v>1200</v>
-      </c>
-    </row>
-    <row r="90" spans="2:8">
-      <c r="B90" s="2" t="n">
-        <v>45374</v>
-      </c>
-      <c r="E90" s="38" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G90" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="91" spans="2:7">
-      <c r="B91" s="2" t="n">
-        <v>45368</v>
-      </c>
-      <c r="G91" s="1" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="92" spans="2:10">
-      <c r="B92" s="2" t="n">
-        <v>45350</v>
-      </c>
-      <c r="E92" s="1" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G92" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H92" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J92" s="32" t="n">
-        <v>50</v>
       </c>
     </row>
     <row r="93" spans="2:8">
       <c r="B93" s="2" t="n">
+        <v>45374</v>
+      </c>
+      <c r="E93" s="38" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G93" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="94" spans="2:7">
+      <c r="B94" s="2" t="n">
+        <v>45368</v>
+      </c>
+      <c r="G94" s="1" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10">
+      <c r="B95" s="2" t="n">
+        <v>45350</v>
+      </c>
+      <c r="E95" s="1" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G95" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J95" s="32" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="96" spans="2:8">
+      <c r="B96" s="2" t="n">
         <v>45329</v>
       </c>
-      <c r="E93" s="1"/>
-      <c r="G93" s="1" t="n">
+      <c r="E96" s="1"/>
+      <c r="G96" s="1" t="n">
         <v>1250</v>
       </c>
-      <c r="H93" s="2"/>
-    </row>
-    <row r="94" spans="2:10">
-      <c r="B94" s="2" t="n">
+      <c r="H96" s="2"/>
+    </row>
+    <row r="97" spans="2:10">
+      <c r="B97" s="2" t="n">
         <v>45309</v>
-      </c>
-      <c r="E94" s="1" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G94" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="J94" s="37" t="n">
-        <v>-50</v>
-      </c>
-    </row>
-    <row r="95" spans="2:7">
-      <c r="B95" s="2" t="n">
-        <v>45297</v>
-      </c>
-      <c r="G95" s="1" t="n">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="96" spans="2:7" s="17" customFormat="1">
-      <c r="B96" s="18"/>
-      <c r="G96" s="19"/>
-    </row>
-    <row r="97" spans="2:8">
-      <c r="B97" s="2" t="n">
-        <v>45272</v>
       </c>
       <c r="E97" s="1" t="n">
         <v>2200</v>
@@ -2154,36 +2257,29 @@
         <v>1000</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="J97" s="37" t="n">
+        <v>-50</v>
       </c>
     </row>
     <row r="98" spans="2:7">
       <c r="B98" s="2" t="n">
-        <v>45268</v>
+        <v>45297</v>
       </c>
       <c r="G98" s="1" t="n">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="99" spans="2:8">
-      <c r="B99" s="2" t="n">
-        <v>45237</v>
-      </c>
-      <c r="E99" s="1" t="n">
-        <v>2200</v>
-      </c>
-      <c r="G99" s="1" t="n">
-        <v>2200</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="100" spans="2:11">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" s="17" customFormat="1">
+      <c r="B99" s="18"/>
+      <c r="G99" s="19"/>
+    </row>
+    <row r="100" spans="2:8">
       <c r="B100" s="2" t="n">
-        <v>45211</v>
-      </c>
-      <c r="E100" s="19" t="n">
+        <v>45272</v>
+      </c>
+      <c r="E100" s="1" t="n">
         <v>2200</v>
       </c>
       <c r="G100" s="1" t="n">
@@ -2192,13 +2288,10 @@
       <c r="H100" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="K100" t="s">
-        <v>54</v>
-      </c>
     </row>
     <row r="101" spans="2:7">
       <c r="B101" s="2" t="n">
-        <v>45206</v>
+        <v>45268</v>
       </c>
       <c r="G101" s="1" t="n">
         <v>1200</v>
@@ -2206,137 +2299,134 @@
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="2" t="n">
+        <v>45237</v>
+      </c>
+      <c r="E102" s="1" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G102" s="1" t="n">
+        <v>2200</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="103" spans="2:11">
+      <c r="B103" s="2" t="n">
+        <v>45211</v>
+      </c>
+      <c r="E103" s="19" t="n">
+        <v>2200</v>
+      </c>
+      <c r="G103" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K103" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="104" spans="2:7">
+      <c r="B104" s="2" t="n">
+        <v>45206</v>
+      </c>
+      <c r="G104" s="1" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="105" spans="2:8">
+      <c r="B105" s="2" t="n">
         <v>45195</v>
       </c>
-      <c r="E102" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="G102" s="1" t="n">
+      <c r="E105" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G105" s="1" t="n">
         <v>650</v>
       </c>
-      <c r="H102" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="103" spans="2:7">
-      <c r="B103" s="2" t="n">
+      <c r="H105" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="106" spans="2:7">
+      <c r="B106" s="2" t="n">
         <v>45187</v>
       </c>
-      <c r="G103" s="1" t="n">
+      <c r="G106" s="1" t="n">
         <v>1500</v>
       </c>
     </row>
-    <row r="104" spans="2:8">
-      <c r="B104" s="2" t="n">
+    <row r="107" spans="2:8">
+      <c r="B107" s="2" t="n">
         <v>45156</v>
       </c>
-      <c r="E104" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="G104" s="1" t="n">
+      <c r="E107" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G107" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="H104" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="105" spans="2:7">
-      <c r="B105" s="2" t="n">
+      <c r="H107" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="108" spans="2:7">
+      <c r="B108" s="2" t="n">
         <v>45153</v>
       </c>
-      <c r="G105" s="1" t="n">
+      <c r="G108" s="1" t="n">
         <v>1150</v>
       </c>
     </row>
-    <row r="106" spans="2:8">
-      <c r="B106" s="2" t="n">
+    <row r="109" spans="2:8">
+      <c r="B109" s="2" t="n">
         <v>45127</v>
       </c>
-      <c r="E106" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="G106" s="1" t="n">
+      <c r="E109" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G109" s="1" t="n">
         <v>650</v>
       </c>
-      <c r="H106" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="107" spans="2:7">
-      <c r="B107" s="2" t="n">
+      <c r="H109" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="110" spans="2:7">
+      <c r="B110" s="2" t="n">
         <v>45123</v>
       </c>
-      <c r="G107" s="1" t="n">
+      <c r="G110" s="1" t="n">
         <v>1500</v>
-      </c>
-    </row>
-    <row r="108" spans="2:8">
-      <c r="B108" s="2" t="n">
-        <v>45093</v>
-      </c>
-      <c r="E108" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="G108" s="1" t="n">
-        <v>500</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="109" spans="2:7">
-      <c r="B109" s="2" t="n">
-        <v>45090</v>
-      </c>
-      <c r="G109" s="1" t="n">
-        <v>1650</v>
-      </c>
-    </row>
-    <row r="110" spans="2:8">
-      <c r="B110" s="2" t="n">
-        <v>45051</v>
-      </c>
-      <c r="E110" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="G110" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="H110" s="2" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="111" spans="2:8">
       <c r="B111" s="2" t="n">
-        <v>45027</v>
+        <v>45093</v>
       </c>
       <c r="E111" s="1" t="n">
         <v>2150</v>
       </c>
       <c r="G111" s="1" t="n">
-        <v>2150</v>
+        <v>500</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="112" spans="2:8">
+    <row r="112" spans="2:7">
       <c r="B112" s="2" t="n">
-        <v>44989</v>
-      </c>
-      <c r="E112" s="1" t="n">
-        <v>2150</v>
+        <v>45090</v>
       </c>
       <c r="G112" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="H112" s="2" t="s">
-        <v>61</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="113" spans="2:8">
       <c r="B113" s="2" t="n">
-        <v>44963</v>
+        <v>45051</v>
       </c>
       <c r="E113" s="1" t="n">
         <v>2150</v>
@@ -2345,191 +2435,197 @@
         <v>2150</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="114" spans="2:8">
       <c r="B114" s="2" t="n">
-        <v>44939</v>
+        <v>45027</v>
       </c>
       <c r="E114" s="1" t="n">
         <v>2150</v>
       </c>
       <c r="G114" s="1" t="n">
-        <v>650</v>
+        <v>2150</v>
       </c>
       <c r="H114" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="115" spans="2:8">
+      <c r="B115" s="2" t="n">
+        <v>44989</v>
+      </c>
+      <c r="E115" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G115" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="H115" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="115" spans="2:7">
-      <c r="B115" s="2" t="n">
-        <v>44930</v>
-      </c>
-      <c r="G115" s="1" t="n">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="116" spans="2:7" s="17" customFormat="1">
-      <c r="B116" s="18"/>
-      <c r="G116" s="19"/>
+    <row r="116" spans="2:8">
+      <c r="B116" s="2" t="n">
+        <v>44963</v>
+      </c>
+      <c r="E116" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G116" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="117" spans="2:8">
       <c r="B117" s="2" t="n">
-        <v>44908</v>
+        <v>44939</v>
       </c>
       <c r="E117" s="1" t="n">
         <v>2150</v>
       </c>
       <c r="G117" s="1" t="n">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="118" spans="2:7">
       <c r="B118" s="2" t="n">
+        <v>44930</v>
+      </c>
+      <c r="G118" s="1" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="119" spans="2:7" s="17" customFormat="1">
+      <c r="B119" s="18"/>
+      <c r="G119" s="19"/>
+    </row>
+    <row r="120" spans="2:8">
+      <c r="B120" s="2" t="n">
+        <v>44908</v>
+      </c>
+      <c r="E120" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G120" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="121" spans="2:7">
+      <c r="B121" s="2" t="n">
         <v>44899</v>
       </c>
-      <c r="G118" s="1" t="n">
+      <c r="G121" s="1" t="n">
         <v>1650</v>
       </c>
     </row>
-    <row r="119" spans="2:8">
-      <c r="B119" s="2" t="n">
+    <row r="122" spans="2:8">
+      <c r="B122" s="2" t="n">
         <v>44873</v>
       </c>
-      <c r="E119" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="G119" s="1" t="n">
+      <c r="E122" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G122" s="1" t="n">
         <v>1000</v>
       </c>
-      <c r="H119" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="120" spans="2:7">
-      <c r="B120" s="2" t="n">
+      <c r="H122" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="123" spans="2:7">
+      <c r="B123" s="2" t="n">
         <v>44869</v>
       </c>
-      <c r="G120" s="1" t="n">
+      <c r="G123" s="1" t="n">
         <v>1150</v>
-      </c>
-    </row>
-    <row r="121" spans="2:8">
-      <c r="B121" s="2" t="n">
-        <v>44852</v>
-      </c>
-      <c r="E121" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="G121" s="1" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="122" spans="2:7">
-      <c r="B122" s="2" t="n">
-        <v>44847</v>
-      </c>
-      <c r="G122" s="1" t="n">
-        <v>1150</v>
-      </c>
-    </row>
-    <row r="123" spans="2:11">
-      <c r="B123" s="2" t="n">
-        <v>44808</v>
-      </c>
-      <c r="E123" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="G123" s="1" t="n">
-        <v>1731</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K123" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="124" spans="2:8">
       <c r="B124" s="2" t="n">
-        <v>44777</v>
+        <v>44852</v>
       </c>
       <c r="E124" s="1" t="n">
         <v>2150</v>
       </c>
       <c r="G124" s="1" t="n">
-        <v>2150</v>
+        <v>1000</v>
       </c>
       <c r="H124" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="125" spans="2:7">
+      <c r="B125" s="2" t="n">
+        <v>44847</v>
+      </c>
+      <c r="G125" s="1" t="n">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="126" spans="2:11">
+      <c r="B126" s="2" t="n">
+        <v>44808</v>
+      </c>
+      <c r="E126" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G126" s="1" t="n">
+        <v>1731</v>
+      </c>
+      <c r="H126" s="2" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="125" spans="2:8">
-      <c r="B125" s="2" t="n">
-        <v>44741</v>
-      </c>
-      <c r="E125" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="G125" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="H125" s="2" t="s">
+      <c r="K126" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="126" spans="2:8">
-      <c r="B126" s="2" t="n">
-        <v>44718</v>
-      </c>
-      <c r="E126" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="G126" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="127" spans="2:8">
       <c r="B127" s="2" t="n">
-        <v>44685</v>
+        <v>44777</v>
       </c>
       <c r="E127" s="1" t="n">
         <v>2150</v>
       </c>
       <c r="G127" s="1" t="n">
-        <v>300</v>
+        <v>2150</v>
       </c>
       <c r="H127" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="128" spans="2:8">
+      <c r="B128" s="2" t="n">
+        <v>44741</v>
+      </c>
+      <c r="E128" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G128" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="H128" s="2" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="128" spans="2:7">
-      <c r="B128" s="2" t="n">
-        <v>44684</v>
-      </c>
-      <c r="G128" s="1" t="n">
-        <v>1850</v>
       </c>
     </row>
     <row r="129" spans="2:8">
       <c r="B129" s="2" t="n">
-        <v>44662</v>
+        <v>44718</v>
       </c>
       <c r="E129" s="1" t="n">
         <v>2150</v>
       </c>
       <c r="G129" s="1" t="n">
-        <v>500</v>
+        <v>2150</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>73</v>
@@ -2537,36 +2633,35 @@
     </row>
     <row r="130" spans="2:8">
       <c r="B130" s="2" t="n">
-        <v>44656</v>
+        <v>44685</v>
+      </c>
+      <c r="E130" s="1" t="n">
+        <v>2150</v>
       </c>
       <c r="G130" s="1" t="n">
-        <v>1650</v>
-      </c>
-      <c r="H130" s="2"/>
-    </row>
-    <row r="131" spans="2:8">
+        <v>300</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="131" spans="2:7">
       <c r="B131" s="2" t="n">
-        <v>44624</v>
-      </c>
-      <c r="E131" s="1" t="n">
-        <v>2150</v>
+        <v>44684</v>
       </c>
       <c r="G131" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>74</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="132" spans="2:8">
       <c r="B132" s="2" t="n">
-        <v>44600</v>
+        <v>44662</v>
       </c>
       <c r="E132" s="1" t="n">
         <v>2150</v>
       </c>
       <c r="G132" s="1" t="n">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>75</v>
@@ -2574,153 +2669,190 @@
     </row>
     <row r="133" spans="2:8">
       <c r="B133" s="2" t="n">
-        <v>44599</v>
-      </c>
-      <c r="E133" s="1"/>
+        <v>44656</v>
+      </c>
       <c r="G133" s="1" t="n">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="H133" s="2"/>
     </row>
     <row r="134" spans="2:8">
       <c r="B134" s="2" t="n">
-        <v>44572</v>
+        <v>44624</v>
       </c>
       <c r="E134" s="1" t="n">
         <v>2150</v>
       </c>
       <c r="G134" s="1" t="n">
-        <v>1000</v>
+        <v>2150</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="135" spans="2:10">
+    <row r="135" spans="2:8">
       <c r="B135" s="2" t="n">
-        <v>44568</v>
-      </c>
-      <c r="E135" s="1"/>
+        <v>44600</v>
+      </c>
+      <c r="E135" s="1" t="n">
+        <v>2150</v>
+      </c>
       <c r="G135" s="1" t="n">
-        <v>1150</v>
-      </c>
-      <c r="H135" s="2"/>
-      <c r="J135" s="6"/>
-    </row>
-    <row r="136" spans="2:10" s="17" customFormat="1">
-      <c r="B136" s="18"/>
-      <c r="E136" s="19"/>
-      <c r="G136" s="19"/>
-      <c r="H136" s="18"/>
-      <c r="J136" s="33"/>
+        <v>550</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="136" spans="2:8">
+      <c r="B136" s="2" t="n">
+        <v>44599</v>
+      </c>
+      <c r="E136" s="1"/>
+      <c r="G136" s="1" t="n">
+        <v>1600</v>
+      </c>
+      <c r="H136" s="2"/>
     </row>
     <row r="137" spans="2:8">
       <c r="B137" s="2" t="n">
+        <v>44572</v>
+      </c>
+      <c r="E137" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G137" s="1" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="138" spans="2:10">
+      <c r="B138" s="2" t="n">
+        <v>44568</v>
+      </c>
+      <c r="E138" s="1"/>
+      <c r="G138" s="1" t="n">
+        <v>1150</v>
+      </c>
+      <c r="H138" s="2"/>
+      <c r="J138" s="6"/>
+    </row>
+    <row r="139" spans="2:10" s="17" customFormat="1">
+      <c r="B139" s="18"/>
+      <c r="E139" s="19"/>
+      <c r="G139" s="19"/>
+      <c r="H139" s="18"/>
+      <c r="J139" s="33"/>
+    </row>
+    <row r="140" spans="2:8">
+      <c r="B140" s="2" t="n">
         <v>44532</v>
       </c>
-      <c r="E137" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="G137" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="138" spans="2:8">
-      <c r="B138" s="2" t="n">
+      <c r="E140" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G140" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="141" spans="2:8">
+      <c r="B141" s="2" t="n">
         <v>44502</v>
       </c>
-      <c r="E138" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="G138" s="1" t="n">
-        <v>2150</v>
-      </c>
-      <c r="H138" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="139" spans="2:8">
-      <c r="B139" s="2" t="n">
+      <c r="E141" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G141" s="1" t="n">
+        <v>2150</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="142" spans="2:8">
+      <c r="B142" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="E139" s="19" t="n">
-        <v>2150</v>
-      </c>
-      <c r="G139" s="1" t="n">
+      <c r="E142" s="19" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G142" s="1" t="n">
         <v>850</v>
       </c>
-      <c r="H139" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="140" spans="2:7">
-      <c r="B140" s="2" t="n">
+      <c r="H142" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="143" spans="2:7">
+      <c r="B143" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="G140" s="1" t="n">
+      <c r="G143" s="1" t="n">
         <v>500</v>
       </c>
     </row>
-    <row r="141" spans="2:7">
-      <c r="B141" s="2" t="n">
+    <row r="144" spans="2:7">
+      <c r="B144" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="G141" s="1" t="n">
+      <c r="G144" s="1" t="n">
         <v>800</v>
       </c>
     </row>
-    <row r="142" spans="2:7" s="17" customFormat="1">
-      <c r="B142" s="18"/>
-      <c r="G142" s="19"/>
-    </row>
-    <row r="143" spans="2:7">
-      <c r="B143" s="2"/>
-      <c r="G143" s="1"/>
-    </row>
-    <row r="144" spans="2:11" s="11" customFormat="1">
-      <c r="B144" s="13" t="n">
+    <row r="145" spans="2:7" s="17" customFormat="1">
+      <c r="B145" s="18"/>
+      <c r="G145" s="19"/>
+    </row>
+    <row r="146" spans="2:7">
+      <c r="B146" s="2"/>
+      <c r="G146" s="1"/>
+    </row>
+    <row r="147" spans="2:11" s="11" customFormat="1">
+      <c r="B147" s="13" t="n">
         <v>44468</v>
       </c>
-      <c r="E144" s="12" t="n">
-        <v>2150</v>
-      </c>
-      <c r="G144" s="12" t="n">
-        <v>2150</v>
-      </c>
-      <c r="H144" s="13"/>
-      <c r="J144" s="12" t="n">
-        <v>2150</v>
-      </c>
-      <c r="K144" s="11" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="145" spans="2:11" s="11" customFormat="1">
-      <c r="B145" s="13" t="n">
+      <c r="E147" s="12" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>2150</v>
+      </c>
+      <c r="H147" s="13"/>
+      <c r="J147" s="12" t="n">
+        <v>2150</v>
+      </c>
+      <c r="K147" s="11" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="148" spans="2:11" s="11" customFormat="1">
+      <c r="B148" s="13" t="n">
         <v>44468</v>
       </c>
-      <c r="E145" s="12" t="n">
-        <v>2150</v>
-      </c>
-      <c r="G145" s="12" t="n">
-        <v>2150</v>
-      </c>
-      <c r="H145" s="13"/>
-      <c r="J145" s="12" t="n">
-        <v>2150</v>
-      </c>
-      <c r="K145" s="11" t="s">
-        <v>80</v>
+      <c r="E148" s="12" t="n">
+        <v>2150</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>2150</v>
+      </c>
+      <c r="H148" s="13"/>
+      <c r="J148" s="12" t="n">
+        <v>2150</v>
+      </c>
+      <c r="K148" s="11" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1783270450" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783280795" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -2729,16 +2861,151 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1783270450" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1783270450" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783270450" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783270450" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1783280795" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783280795" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783280795" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783280795" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783270450" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783280795" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="9" defaultColWidth="10.000000" defaultRowHeight="15.40"/>
+  <cols>
+    <col min="1" max="1" width="19.839286" customWidth="1"/>
+    <col min="2" max="2" width="30.366071" customWidth="1"/>
+    <col min="3" max="3" width="18.678571" customWidth="1"/>
+    <col min="4" max="4" width="22.455357" customWidth="1"/>
+    <col min="5" max="5" width="15.223214" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" s="61" customFormat="1">
+      <c r="A2" s="62" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="61" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="62" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="62" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="59" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C3" s="24" t="n">
+        <v>10669</v>
+      </c>
+      <c r="E3" s="63" t="n">
+        <v>10669</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="59" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="60" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D4" s="64" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E4" s="24" t="n">
+        <v>11969</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="59" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="60" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D5" s="64" t="n">
+        <v>1300</v>
+      </c>
+      <c r="E5" s="24" t="n">
+        <v>12969</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="59" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="60" t="n">
+        <v>2300</v>
+      </c>
+      <c r="D6" s="64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="24" t="n">
+        <v>15269</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783280795" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="1.000000" right="1.000000" top="1.000000" bottom="1.000000" header="0.393750" footer="0.393750"/>
+  <pageSetup paperSize="1" fitToWidth="0" fitToHeight="1" pageOrder="overThenDown"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1783280795" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783280795" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783280795" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783280795" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783280795" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/data/ltb/Kayak ending rental fee.xlsx
+++ b/data/ltb/Kayak ending rental fee.xlsx
@@ -5,26 +5,28 @@
   <fileSharing readOnlyRecommended="0" userName="KwGo"/>
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="1" xWindow="240" yWindow="60" windowWidth="14805" windowHeight="8010" tabRatio="500"/>
+    <workbookView activeTab="3" xWindow="240" yWindow="60" windowWidth="14805" windowHeight="8010" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Kayak Rent Details" sheetId="1" r:id="rId4"/>
     <sheet name="Rent Ledger" sheetId="2" r:id="rId5"/>
+    <sheet name="Rent Summary" sheetId="3" r:id="rId6"/>
+    <sheet name="LTB Application Fee" sheetId="4" r:id="rId7"/>
   </sheets>
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1783280795" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1783280795" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1783280795" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1783280795"/>
+      <pm:revision xmlns:pm="smNativeData" day="1783282349" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1783282349" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" printCurSheet="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1783282349" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1783282349"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="111">
   <si>
     <t>Paid date</t>
   </si>
@@ -306,6 +308,57 @@
   </si>
   <si>
     <t>Final Balance Owing: $15269.00</t>
+  </si>
+  <si>
+    <t>Rent Summary</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Arrears at filing</t>
+  </si>
+  <si>
+    <t>New rent (May–July)</t>
+  </si>
+  <si>
+    <t>Payments received</t>
+  </si>
+  <si>
+    <t>Current arrears</t>
+  </si>
+  <si>
+    <t>Filing fee</t>
+  </si>
+  <si>
+    <t>Grand total</t>
+  </si>
+  <si>
+    <t>LTB Application Fee Receipt</t>
+  </si>
+  <si>
+    <t>Detail</t>
+  </si>
+  <si>
+    <t>File Number</t>
+  </si>
+  <si>
+    <t>LTB-L-042466-26</t>
+  </si>
+  <si>
+    <t>Payment Code</t>
+  </si>
+  <si>
+    <t>P0017229</t>
+  </si>
+  <si>
+    <t>Payment Type</t>
+  </si>
+  <si>
+    <t>Online</t>
   </si>
 </sst>
 </file>
@@ -338,7 +391,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783280795" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783282349" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -353,7 +406,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783280795" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783282349" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -375,7 +428,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="85" fgClr="00FFFFFF" bgLvl="15" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="85" fgClr="00FFFFFF" bgLvl="15" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -386,7 +439,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="64" fgClr="0000FF00" bgLvl="36" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="64" fgClr="0000FF00" bgLvl="36" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -397,7 +450,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="12" fgClr="000000FF" bgLvl="88" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="12" fgClr="000000FF" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -408,7 +461,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="12" fgClr="00FF0000" bgLvl="88" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="12" fgClr="00FF0000" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -419,7 +472,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="12" fgClr="0000FFFF" bgLvl="88" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="12" fgClr="0000FFFF" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -430,7 +483,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -441,7 +494,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -452,7 +505,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="12" fgClr="00FFFF00" bgLvl="88" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="12" fgClr="00FFFF00" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -463,7 +516,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -474,7 +527,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="100" fgClr="00FFE0E0" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="100" fgClr="00FFE0E0" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -485,7 +538,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783280795" type="1" fgLvl="12" fgClr="007F7F00" bgLvl="88" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="12" fgClr="007F7F00" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -507,7 +560,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
+          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
         </ext>
       </extLst>
     </border>
@@ -526,7 +579,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
+          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
         </ext>
       </extLst>
     </border>
@@ -545,7 +598,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
+          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
         </ext>
       </extLst>
     </border>
@@ -564,7 +617,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
+          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
         </ext>
       </extLst>
     </border>
@@ -583,7 +636,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
+          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
         </ext>
       </extLst>
     </border>
@@ -602,7 +655,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
+          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
         </ext>
       </extLst>
     </border>
@@ -621,7 +674,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
+          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
         </ext>
       </extLst>
     </border>
@@ -640,7 +693,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
+          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
         </ext>
       </extLst>
     </border>
@@ -659,7 +712,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
+          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
         </ext>
       </extLst>
     </border>
@@ -678,7 +731,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
+          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
         </ext>
       </extLst>
     </border>
@@ -697,7 +750,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
+          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
         </ext>
       </extLst>
     </border>
@@ -716,7 +769,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783280795"/>
+          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
         </ext>
       </extLst>
     </border>
@@ -724,7 +777,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -800,6 +853,23 @@
     </xf>
     <xf numFmtId="170" fontId="0" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -807,10 +877,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1783280795" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1783282349" count="1">
         <pm:charStyle name="Normal" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1783280795" count="15">
+      <pm:colors xmlns:pm="smNativeData" id="1783282349" count="15">
         <pm:color name="Color 24" rgb="D9D9D9"/>
         <pm:color name="Color 25" rgb="474747"/>
         <pm:color name="Color 26" rgb="5C5CFF"/>
@@ -2852,7 +2922,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1783280795" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783282349" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -2861,16 +2931,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1783280795" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1783280795" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783280795" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783280795" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1783282349" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783282349" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783282349" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783282349" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783280795" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783282349" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -2987,7 +3057,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1783280795" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783282349" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -2996,16 +3066,209 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1783280795" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1783280795" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783280795" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783280795" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1783282349" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783282349" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783282349" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783282349" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783280795" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783282349" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="9" defaultColWidth="10.000000" defaultRowHeight="15.40"/>
+  <cols>
+    <col min="1" max="1" width="26.875000" customWidth="1"/>
+    <col min="2" max="2" width="18.437500" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="66" customFormat="1">
+      <c r="A3" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="68" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="24" t="n">
+        <v>10669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B5" s="24" t="n">
+        <v>6900</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="67" t="n">
+        <v>-2300</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <v>15269</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="65" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9" s="24" t="n">
+        <v>16455</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783282349" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="1.000000" right="1.000000" top="1.000000" bottom="1.000000" header="0.393750" footer="0.393750"/>
+  <pageSetup paperSize="1" fitToWidth="0" fitToHeight="1" pageOrder="overThenDown"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1783282349" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783282349" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783282349" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783282349" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783282349" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="9" defaultColWidth="10.000000" defaultRowHeight="15.40"/>
+  <cols>
+    <col min="1" max="16384" width="29.419643" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="72" customFormat="1">
+      <c r="A3" s="72" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="73" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="69" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B5" s="71" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6" s="71" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="71" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="70" t="n">
+        <v>46156</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783282349" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="1.000000" right="1.000000" top="1.000000" bottom="1.000000" header="0.393750" footer="0.393750"/>
+  <pageSetup paperSize="1" fitToWidth="0" fitToHeight="1" pageOrder="overThenDown"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1783282349" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783282349" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783282349" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783282349" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783282349" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>

--- a/data/ltb/Kayak ending rental fee.xlsx
+++ b/data/ltb/Kayak ending rental fee.xlsx
@@ -5,7 +5,7 @@
   <fileSharing readOnlyRecommended="0" userName="KwGo"/>
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="3" xWindow="240" yWindow="60" windowWidth="14805" windowHeight="8010" tabRatio="500"/>
+    <workbookView activeTab="1" xWindow="240" yWindow="60" windowWidth="14805" windowHeight="8010" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Kayak Rent Details" sheetId="1" r:id="rId4"/>
@@ -16,17 +16,17 @@
   <calcPr/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:revision xmlns:pm="smNativeData" day="1783282349" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
-      <pm:docPrefs xmlns:pm="smNativeData" id="1783282349" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" printCurSheet="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
-      <pm:compatibility xmlns:pm="smNativeData" id="1783282349" overlapCells="1"/>
-      <pm:defCurrency xmlns:pm="smNativeData" id="1783282349"/>
+      <pm:revision xmlns:pm="smNativeData" day="1783289634" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1783289634" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" printCurSheet="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1783289634" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1783289634"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="110">
   <si>
     <t>Paid date</t>
   </si>
@@ -298,16 +298,13 @@
     <t>Previous arrears balance</t>
   </si>
   <si>
-    <t>May rent charged</t>
-  </si>
-  <si>
     <t>June rent charged</t>
   </si>
   <si>
     <t>July rent charged</t>
   </si>
   <si>
-    <t>Final Balance Owing: $15269.00</t>
+    <t>Final Balance Owing: $13969.00</t>
   </si>
   <si>
     <t>Rent Summary</t>
@@ -322,7 +319,7 @@
     <t>Arrears at filing</t>
   </si>
   <si>
-    <t>New rent (May–July)</t>
+    <t>New rent (June–July)</t>
   </si>
   <si>
     <t>Payments received</t>
@@ -391,7 +388,7 @@
       <sz val="11"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783282349" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783289634" ulstyle="none" kern="1">
             <pm:latin face="Calibri" sz="220" lang="default"/>
             <pm:cs face="Times New Roman" sz="220" lang="default"/>
             <pm:ea face="SimSun" sz="220" lang="default"/>
@@ -406,7 +403,7 @@
       <sz val="10"/>
       <extLst>
         <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783282349" ulstyle="none" kern="1">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783289634" ulstyle="none" kern="1">
             <pm:latin face="Arial" sz="200" lang="default"/>
             <pm:cs face="Times New Roman" sz="200" lang="default"/>
             <pm:ea face="SimSun" sz="200" lang="default"/>
@@ -428,7 +425,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="85" fgClr="00FFFFFF" bgLvl="15" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783289634" type="1" fgLvl="85" fgClr="00FFFFFF" bgLvl="15" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -439,7 +436,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="64" fgClr="0000FF00" bgLvl="36" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783289634" type="1" fgLvl="64" fgClr="0000FF00" bgLvl="36" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -450,7 +447,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="12" fgClr="000000FF" bgLvl="88" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783289634" type="1" fgLvl="12" fgClr="000000FF" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -461,7 +458,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="12" fgClr="00FF0000" bgLvl="88" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783289634" type="1" fgLvl="12" fgClr="00FF0000" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -472,7 +469,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="12" fgClr="0000FFFF" bgLvl="88" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783289634" type="1" fgLvl="12" fgClr="0000FFFF" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -483,7 +480,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783289634" type="1" fgLvl="38" fgClr="00FFFF00" bgLvl="62" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -494,7 +491,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783289634" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
           </ext>
         </extLst>
       </patternFill>
@@ -505,7 +502,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="12" fgClr="00FFFF00" bgLvl="88" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783289634" type="1" fgLvl="12" fgClr="00FFFF00" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -516,7 +513,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783289634" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -527,7 +524,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="100" fgClr="00FFE0E0" bgLvl="0" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783289634" type="1" fgLvl="100" fgClr="00FFE0E0" bgLvl="0" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -538,7 +535,7 @@
         <bgColor rgb="FFFFFFFF"/>
         <extLst>
           <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783282349" type="1" fgLvl="12" fgClr="007F7F00" bgLvl="88" bgClr="00FFFFFF"/>
+            <pm:shade xmlns:pm="smNativeData" id="1783289634" type="1" fgLvl="12" fgClr="007F7F00" bgLvl="88" bgClr="00FFFFFF"/>
           </ext>
         </extLst>
       </patternFill>
@@ -560,7 +557,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
+          <pm:border xmlns:pm="smNativeData" id="1783289634"/>
         </ext>
       </extLst>
     </border>
@@ -579,7 +576,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
+          <pm:border xmlns:pm="smNativeData" id="1783289634"/>
         </ext>
       </extLst>
     </border>
@@ -598,7 +595,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
+          <pm:border xmlns:pm="smNativeData" id="1783289634"/>
         </ext>
       </extLst>
     </border>
@@ -617,7 +614,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
+          <pm:border xmlns:pm="smNativeData" id="1783289634"/>
         </ext>
       </extLst>
     </border>
@@ -636,7 +633,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
+          <pm:border xmlns:pm="smNativeData" id="1783289634"/>
         </ext>
       </extLst>
     </border>
@@ -655,7 +652,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
+          <pm:border xmlns:pm="smNativeData" id="1783289634"/>
         </ext>
       </extLst>
     </border>
@@ -674,7 +671,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
+          <pm:border xmlns:pm="smNativeData" id="1783289634"/>
         </ext>
       </extLst>
     </border>
@@ -693,7 +690,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
+          <pm:border xmlns:pm="smNativeData" id="1783289634"/>
         </ext>
       </extLst>
     </border>
@@ -712,7 +709,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
+          <pm:border xmlns:pm="smNativeData" id="1783289634"/>
         </ext>
       </extLst>
     </border>
@@ -731,7 +728,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
+          <pm:border xmlns:pm="smNativeData" id="1783289634"/>
         </ext>
       </extLst>
     </border>
@@ -750,7 +747,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
+          <pm:border xmlns:pm="smNativeData" id="1783289634"/>
         </ext>
       </extLst>
     </border>
@@ -769,7 +766,7 @@
       </bottom>
       <extLst>
         <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783282349"/>
+          <pm:border xmlns:pm="smNativeData" id="1783289634"/>
         </ext>
       </extLst>
     </border>
@@ -777,7 +774,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -837,37 +834,17 @@
     <xf numFmtId="165" fontId="0" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="170" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="170" fontId="0" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1"/>
-    <xf numFmtId="170" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="0" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1"/>
     <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="11" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -877,10 +854,10 @@
   <tableStyles count="0"/>
   <extLst>
     <ext uri="smNativeData">
-      <pm:charStyles xmlns:pm="smNativeData" id="1783282349" count="1">
+      <pm:charStyles xmlns:pm="smNativeData" id="1783289634" count="1">
         <pm:charStyle name="Normal" fontId="0" Id="1"/>
       </pm:charStyles>
-      <pm:colors xmlns:pm="smNativeData" id="1783282349" count="15">
+      <pm:colors xmlns:pm="smNativeData" id="1783289634" count="15">
         <pm:color name="Color 24" rgb="D9D9D9"/>
         <pm:color name="Color 25" rgb="474747"/>
         <pm:color name="Color 26" rgb="5C5CFF"/>
@@ -1194,17 +1171,17 @@
       </c>
     </row>
     <row r="5" spans="2:11" s="16" customFormat="1">
-      <c r="B5" s="58" t="n">
+      <c r="B5" s="15" t="n">
         <v>46208</v>
       </c>
-      <c r="D5" s="58" t="n">
+      <c r="D5" s="15" t="n">
         <v>46208</v>
       </c>
       <c r="I5" s="23" t="s">
         <v>5</v>
       </c>
       <c r="J5" s="28" t="n">
-        <v>-15269</v>
+        <v>-13969</v>
       </c>
       <c r="K5" s="16" t="s">
         <v>6</v>
@@ -1213,7 +1190,7 @@
     <row r="6" spans="1:14" s="25" customFormat="1">
       <c r="A6" s="42"/>
       <c r="B6" s="35"/>
-      <c r="E6" s="57" t="n">
+      <c r="E6" s="36" t="n">
         <v>2300</v>
       </c>
       <c r="G6" s="34" t="n">
@@ -1240,7 +1217,7 @@
       <c r="G7" s="38" t="n">
         <v>500</v>
       </c>
-      <c r="H7" s="54" t="s">
+      <c r="H7" s="16" t="s">
         <v>9</v>
       </c>
       <c r="J7" s="28" t="n">
@@ -1322,10 +1299,10 @@
       </c>
     </row>
     <row r="14" spans="2:11" s="16" customFormat="1">
-      <c r="B14" s="58" t="n">
+      <c r="B14" s="15" t="n">
         <v>46157</v>
       </c>
-      <c r="D14" s="58" t="n">
+      <c r="D14" s="15" t="n">
         <v>46157</v>
       </c>
       <c r="I14" s="23" t="s">
@@ -1356,28 +1333,28 @@
       <c r="G18" s="19"/>
       <c r="N18" s="30"/>
     </row>
-    <row r="19" spans="2:14" s="51" customFormat="1">
-      <c r="B19" s="52" t="n">
+    <row r="19" spans="2:14" s="39" customFormat="1">
+      <c r="B19" s="51" t="n">
         <v>46149</v>
       </c>
-      <c r="E19" s="53" t="n">
+      <c r="E19" s="52" t="n">
         <v>2300</v>
       </c>
       <c r="G19" s="43" t="n">
         <v>1000</v>
       </c>
-      <c r="H19" s="51" t="s">
+      <c r="H19" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="J19" s="55" t="n">
+      <c r="J19" s="28" t="n">
         <v>-1300</v>
       </c>
-      <c r="K19" s="56" t="s">
+      <c r="K19" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="L19" s="53"/>
-      <c r="M19" s="53"/>
-      <c r="N19" s="53"/>
+      <c r="L19" s="52"/>
+      <c r="M19" s="52"/>
+      <c r="N19" s="52"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="2" t="n">
@@ -1389,7 +1366,7 @@
       <c r="H20" t="s">
         <v>13</v>
       </c>
-      <c r="J20" s="55" t="n">
+      <c r="J20" s="28" t="n">
         <v>-1000</v>
       </c>
       <c r="K20" s="36" t="s">
@@ -1707,10 +1684,10 @@
       </c>
     </row>
     <row r="49" spans="2:11" s="16" customFormat="1">
-      <c r="B49" s="58" t="n">
+      <c r="B49" s="15" t="n">
         <v>46333</v>
       </c>
-      <c r="D49" s="58" t="n">
+      <c r="D49" s="15" t="n">
         <v>46333</v>
       </c>
       <c r="I49" s="23" t="s">
@@ -2922,7 +2899,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1783282349" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783289634" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -2931,16 +2908,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1783282349" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1783282349" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783282349" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783282349" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1783289634" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783289634" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783289634" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783289634" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783282349" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783289634" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -2951,14 +2928,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="9" defaultColWidth="10.000000" defaultRowHeight="15.40"/>
   <cols>
-    <col min="1" max="1" width="19.839286" customWidth="1"/>
-    <col min="2" max="2" width="30.366071" customWidth="1"/>
-    <col min="3" max="3" width="18.678571" customWidth="1"/>
-    <col min="4" max="4" width="22.455357" customWidth="1"/>
-    <col min="5" max="5" width="15.223214" customWidth="1"/>
+    <col min="1" max="1" width="12.875000" customWidth="1"/>
+    <col min="2" max="2" width="25.008929" customWidth="1"/>
+    <col min="3" max="3" width="11.714286" customWidth="1"/>
+    <col min="4" max="4" width="11.205357" customWidth="1"/>
+    <col min="5" max="5" width="13.616071" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
@@ -2966,26 +2943,26 @@
         <v>83</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="61" customFormat="1">
-      <c r="A2" s="62" t="s">
+    <row r="2" spans="1:5" s="54" customFormat="1">
+      <c r="A2" s="55" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="54" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="55" t="s">
         <v>86</v>
       </c>
-      <c r="D2" s="62" t="s">
+      <c r="D2" s="55" t="s">
         <v>87</v>
       </c>
-      <c r="E2" s="62" t="s">
+      <c r="E2" s="55" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="59" t="n">
-        <v>46157</v>
+      <c r="A3" s="53" t="n">
+        <v>46156</v>
       </c>
       <c r="B3" t="s">
         <v>89</v>
@@ -2993,71 +2970,54 @@
       <c r="C3" s="24" t="n">
         <v>10669</v>
       </c>
-      <c r="E3" s="63" t="n">
+      <c r="E3" s="52" t="n">
         <v>10669</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="59" t="n">
-        <v>46027</v>
+      <c r="A4" s="53" t="n">
+        <v>46028</v>
       </c>
       <c r="B4" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="60" t="n">
+      <c r="C4" s="24" t="n">
         <v>2300</v>
       </c>
-      <c r="D4" s="64" t="n">
-        <v>1000</v>
+      <c r="D4" s="24" t="n">
+        <v>1300</v>
       </c>
       <c r="E4" s="24" t="n">
-        <v>11969</v>
+        <v>11669</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="59" t="n">
-        <v>46028</v>
+      <c r="A5" s="53" t="n">
+        <v>46029</v>
       </c>
       <c r="B5" t="s">
         <v>91</v>
       </c>
-      <c r="C5" s="60" t="n">
+      <c r="C5" s="24" t="n">
         <v>2300</v>
       </c>
-      <c r="D5" s="64" t="n">
-        <v>1300</v>
+      <c r="D5" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="E5" s="24" t="n">
-        <v>12969</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="59" t="n">
-        <v>46029</v>
-      </c>
-      <c r="B6" t="s">
+        <v>13969</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
         <v>92</v>
-      </c>
-      <c r="C6" s="60" t="n">
-        <v>2300</v>
-      </c>
-      <c r="D6" s="64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="24" t="n">
-        <v>15269</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1783282349" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783289634" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -3066,16 +3026,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1783282349" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1783282349" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783282349" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783282349" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1783289634" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783289634" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783289634" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783289634" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783282349" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783289634" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -3095,20 +3055,20 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="54" customFormat="1">
+      <c r="A3" s="54" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" s="66" customFormat="1">
-      <c r="A3" s="66" t="s">
+      <c r="B3" s="55" t="s">
         <v>95</v>
-      </c>
-      <c r="B3" s="68" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B4" s="24" t="n">
         <v>10669</v>
@@ -3116,49 +3076,49 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B5" s="24" t="n">
-        <v>6900</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B6" s="67" t="n">
-        <v>-2300</v>
+        <v>98</v>
+      </c>
+      <c r="B6" s="56" t="n">
+        <v>-1300</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B7" s="24" t="n">
-        <v>15269</v>
+        <v>13969</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>101</v>
-      </c>
-      <c r="B8" s="65" t="n">
+        <v>100</v>
+      </c>
+      <c r="B8" s="24" t="n">
         <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B9" s="24" t="n">
-        <v>16455</v>
+        <v>14155</v>
       </c>
     </row>
   </sheetData>
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1783282349" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783289634" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -3167,16 +3127,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1783282349" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1783282349" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783282349" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783282349" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1783289634" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783289634" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783289634" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783289634" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783282349" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783289634" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
@@ -3195,54 +3155,54 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="54" customFormat="1">
+      <c r="A3" s="54" t="s">
+        <v>94</v>
+      </c>
+      <c r="B3" s="55" t="s">
         <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" s="72" customFormat="1">
-      <c r="A3" s="72" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="73" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B4" s="69" t="n">
+        <v>95</v>
+      </c>
+      <c r="B4" s="24" t="n">
         <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B5" s="57" t="s">
         <v>105</v>
-      </c>
-      <c r="B5" s="71" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="57" t="s">
         <v>107</v>
-      </c>
-      <c r="B6" s="71" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="57" t="s">
         <v>109</v>
-      </c>
-      <c r="B7" s="71" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>84</v>
       </c>
-      <c r="B8" s="70" t="n">
+      <c r="B8" s="53" t="n">
         <v>46156</v>
       </c>
     </row>
@@ -3250,7 +3210,7 @@
   <printOptions>
     <extLst>
       <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1783282349" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783289634" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
       </ext>
     </extLst>
   </printOptions>
@@ -3259,16 +3219,16 @@
   <headerFooter>
     <extLst>
       <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1783282349" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1783282349" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783282349" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783282349" Id="1" type="0" value="0"/>
+        <pm:header xmlns:pm="smNativeData" id="1783289634" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783289634" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783289634" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783289634" Id="1" type="0" value="0"/>
       </ext>
     </extLst>
   </headerFooter>
   <extLst>
     <ext uri="smNativeData">
-      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783282349" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783289634" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
         <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
         <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
       </pm:sheetPrefs>
